--- a/questionnaire_templates/031_parent_coaching_intake_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/031_parent_coaching_intake_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_1</t>
+          <t>introduction_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parenting Goals</t>
+          <t>What are your parenting goals for your child?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_2</t>
+          <t>introduction_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Family Information</t>
+          <t>How would you like to be contacted for future sessions?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_3</t>
+          <t>family_information_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Parental Stress</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>How often do you feel stressed?</t>
-        </is>
-      </c>
+          <t>Family Information</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_4</t>
+          <t>family_information_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Parental Goals</t>
+          <t>Who lives in the household?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_5</t>
+          <t>parental_support_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Session Details</t>
+          <t>How do you typically support your child's emotional needs?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_6</t>
+          <t>parental_support_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Parent Support</t>
+          <t>Do you have a support system in place for emotional support?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_7</t>
+          <t>parental_support_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Parenting Goals</t>
+          <t>What kind of support do you receive from family members or friends?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_8</t>
+          <t>parenting_goals_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>What specific parenting goals do you want to work on?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_9</t>
+          <t>parenting_goals_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>How would you like to achieve these goals?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_10</t>
+          <t>parent_information_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Parent Information</t>
+          <t>How long have you been a parent?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_11</t>
+          <t>parent_information_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Parental Support</t>
+          <t>What is your child's age and grade level?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_12</t>
+          <t>session_details_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Parental Support</t>
+          <t>How many sessions would you like to schedule?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_13</t>
+          <t>session_details_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Parental Goals</t>
+          <t>What date and time would you prefer for the sessions?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -818,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_14</t>
+          <t>parenting_style_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Parenting Goals</t>
+          <t>How would you describe your parenting style?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_15</t>
+          <t>parenting_style_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Parent Information</t>
+          <t>Do you have any parenting books or resources that you find helpful?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -869,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_16</t>
+          <t>parental_stress_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Parenting Style</t>
+          <t>How often do you experience stress as a parent?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_17</t>
+          <t>parental_stress_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Parent Support System</t>
+          <t>What specific situations or events cause you the most stress?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_18</t>
+          <t>parental_support_1_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Session Details</t>
+          <t>Who do you rely on for emotional support?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -938,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_19</t>
+          <t>parental_support_2_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parental Stress</t>
+          <t>Do you feel supported by your partner or spouse?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -961,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_20</t>
+          <t>parental_goals_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Parental Support</t>
+          <t>What specific goals do you have for your child's development?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -979,17 +975,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_21</t>
+          <t>parental_goals_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Parental Goals</t>
+          <t>How will you support your child in achieving these goals?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1002,17 +998,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_22</t>
+          <t>parenting_strategies_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Parental Goals</t>
+          <t>What strategies do you currently use to manage your child's behavior?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_23</t>
+          <t>parenting_strategies_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Parenting Style</t>
+          <t>How do you handle discipline and setting boundaries?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_24</t>
+          <t>session_details_2_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Parental Stress</t>
+          <t>How will you use the coaching sessions to achieve your goals?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_25</t>
+          <t>session_details_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Parental Stress</t>
+          <t>What specific issues would you like to address in our sessions?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,289 +1126,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_2_choices</t>
+          <t>family_information_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_2_choices</t>
+          <t>family_information_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_4_choices</t>
+          <t>family_information_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_4_choices</t>
+          <t>parent_information_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_4_choices</t>
+          <t>parent_information_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>3-5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>3-5 years</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_13_choices</t>
+          <t>parent_information_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>6-8_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>6-8 years</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_13_choices</t>
+          <t>parent_information_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>9-11_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>9-11 years</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>parent_coaching_intake_survey_13_choices</t>
+          <t>parent_information_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>12+_years</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_14_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_14_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_14_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_21_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_21_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_21_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_22_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_22_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>parent_coaching_intake_survey_22_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>12+ years</t>
         </is>
       </c>
     </row>
